--- a/coronavirus_response_forms/012_mask_request_form--coronavirus_response_forms.xlsx
+++ b/coronavirus_response_forms/012_mask_request_form--coronavirus_response_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -688,8 +688,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -717,12 +717,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'physicians',_'label':_'physicians'}</t>
+          <t>physicians</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Physicians', 'label': 'Physicians'}</t>
+          <t>Physicians</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'nurses',_'label':_'nurses'}</t>
+          <t>nurses</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Nurses', 'label': 'Nurses'}</t>
+          <t>Nurses</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'hospitals',_'label':_'hospitals'}</t>
+          <t>hospitals</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Hospitals', 'label': 'Hospitals'}</t>
+          <t>Hospitals</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'first_responders',_'label':_'first_responders'}</t>
+          <t>first_responders</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'First Responders', 'label': 'First Responders'}</t>
+          <t>First Responders</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'n95',_'label':_'n95'}</t>
+          <t>n95</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'N95', 'label': 'N95'}</t>
+          <t>N95</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'n99',_'label':_'n99'}</t>
+          <t>n99</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'N99', 'label': 'N99'}</t>
+          <t>N99</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'n100',_'label':_'n100'}</t>
+          <t>n100</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'N100', 'label': 'N100'}</t>
+          <t>N100</t>
         </is>
       </c>
     </row>
